--- a/InstantRetail/Tier3-4Strategy/05-analysis-workbook.xlsx
+++ b/InstantRetail/Tier3-4Strategy/05-analysis-workbook.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="AX-A1 10-City Comparison" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AX-A2 3-City Paths" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AX-A3 Contraction Analysis" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Assumptions &amp; Sources" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Case Charts Insights" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AX-A2 3-City Paths" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="AX-A3 Contraction Analysis" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Assumptions &amp; Sources" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,8 +77,16 @@
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -124,6 +133,11 @@
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE599"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -140,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -200,6 +214,20 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1467,6 +1495,420 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Case Charts — O2O竞争格局关键洞察</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>来源: Reports/ (3份case补充信息图) | 日期: 2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>O2O渗透率：市场红利仍在</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>2020年</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>当前</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>变化</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>战略含义</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>O2O在零售消费中的渗透率</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>+24pp</t>
+        </is>
+      </c>
+      <c r="E6" s="29" t="inlineStr">
+        <is>
+          <t>即时零售已是半壁江山；市场不是问题，单位经济是问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>即时零售双核竞争模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>竞争模式</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>代表品牌</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>商业模式</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>核心指标</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Instant Retail关系</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>前置仓（自营）</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>叮咚买菜、朴朴、小象超市</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>买断式自营；平台承担库存和损耗</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>CAGR 30%；品类：生鲜/食品深度</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>品类重叠度**低于**闪电仓；但在快速补货场景有竞争</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="30" t="inlineStr">
+        <is>
+          <t>闪电仓（平台）</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>美团闪购、淘宝闪购、京东秒送</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>平台合作式；连接商家库存</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>SKU 3,000-10,000个；覆盖30K→100K仓库</t>
+        </is>
+      </c>
+      <c r="E11" s="30" t="inlineStr">
+        <is>
+          <t>Instant Retail**主要竞争对手**——同在快速补货和夜间/懒人场景直接竞争</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>线下超市</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>沃尔玛、华润、大润发、便利店</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>传统线下门店</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>占订单60-70%</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>**真正的替代竞争对手**——即时配送差异化vs线下便捷性</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>6大消费场景（渠道竞争矩阵）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>购物任务</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>渠道</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>Instant Retail机会</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>快速补货</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>计划性</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>O2O</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>核心场景——30分钟配送差异化最高；大超合作提升AOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>夜间/懒人/急用</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>非计划性</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>O2O</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>高价值场景——即时需求溢价高；补贴精准化最佳场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>超便捷</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>非计划性</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>线下主导——Instant Retail渗透困难；避免在此场景打补贴战</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>一站式购物</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>计划性</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>线下主导——Instant Retail不适合替代；收缩</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>长尾急用</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>计划性</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>线上</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>线上主导——快递次日达 vs 30分钟即时需求不同</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>冲动尝鲜</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>非计划性</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>线上</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>兴趣电商主导——Instant Retail无优势</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>核心战略洞察</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>1. 即时零售的价值主张是"30分钟配送"（vs线下：更便捷；vs纯线上：更快），不是"更便宜"</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>2. 若补贴用于与线下超市比价格，则补贴永远不能停——战略方向应是从"价格竞争"转向"服务差异化"</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>3. 美团2023年已转向盈利优先，2019-2021年大规模补贴战已过——三四线城市竞争窗口期仍在</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>4. 线下超市（60-70%订单）才是真正的替代竞争对手——Instant Retail的差异化是30分钟 vs 线下"亲自到店"</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>5. 前置仓（自营）vs 闪电仓（平台）的竞争格局意味着：Instant Retail不需要在所有品类与前置仓竞争，只需在自己的核心场景（快速补货/夜间）建立壁垒</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2052,7 +2494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2460,7 +2902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/InstantRetail/Tier3-4Strategy/05-analysis-workbook.xlsx
+++ b/InstantRetail/Tier3-4Strategy/05-analysis-workbook.xlsx
@@ -13,6 +13,7 @@
     <sheet name="AX-A2 3-City Paths" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="AX-A3 Contraction Analysis" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Assumptions &amp; Sources" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="AX-A4 EBIT Model" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,8 +22,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="14">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,8 +90,28 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -138,6 +163,26 @@
         <fgColor rgb="00FFE599"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00404040"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -154,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -228,6 +273,61 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3332,4 +3432,869 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>AX-A4: 3+3+4 城市分组 EBIT 3年情景模型</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>目标：验证 3城聚焦 策略在保守/基准/乐观情景下 3年EBIT路径  |  关键假设：见 Assumptions &amp; Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>SECTION 1: 城市分组（3+3+4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>日均单量(万)</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>AOV(元)</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>履约成本</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="inlineStr">
+        <is>
+          <t>补贴</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>高价值用户%</t>
+        </is>
+      </c>
+      <c r="H5" s="36" t="inlineStr">
+        <is>
+          <t>年亏损(万)</t>
+        </is>
+      </c>
+      <c r="I5" s="36" t="inlineStr">
+        <is>
+          <t>EBIT驱动因子</t>
+        </is>
+      </c>
+      <c r="J5" s="36" t="inlineStr">
+        <is>
+          <t>优先行动</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>聚焦组</t>
+        </is>
+      </c>
+      <c r="B6" s="38" t="inlineStr">
+        <is>
+          <t>泉州+惠州+威海</t>
+        </is>
+      </c>
+      <c r="C6" s="39" t="n">
+        <v>29</v>
+      </c>
+      <c r="D6" s="40" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="E6" s="40" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F6" s="41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G6" s="37" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="H6" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="38" t="inlineStr">
+        <is>
+          <t>AOV↑+补贴压降+规模效应</t>
+        </is>
+      </c>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>全力扶持</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>优化组</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>徐州+南昌+南宁</t>
+        </is>
+      </c>
+      <c r="C7" s="44" t="n">
+        <v>29</v>
+      </c>
+      <c r="D7" s="45" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="E7" s="45" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F7" s="46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G7" s="42" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="H7" s="43" t="n">
+        <v>-4500</v>
+      </c>
+      <c r="I7" s="43" t="inlineStr">
+        <is>
+          <t>补贴精准化+品类优化</t>
+        </is>
+      </c>
+      <c r="J7" s="43" t="inlineStr">
+        <is>
+          <t>精细化运营</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>观察组</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>桂林+赣州+洛阳+宜昌</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" s="45" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="E8" s="45" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F8" s="46" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G8" s="42" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="H8" s="43" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="I8" s="43" t="inlineStr">
+        <is>
+          <t>部分收缩+验证期</t>
+        </is>
+      </c>
+      <c r="J8" s="43" t="inlineStr">
+        <is>
+          <t>选择性收缩</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="8" customHeight="1"/>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>SECTION 2: 情景假设（年化改善率）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="36" t="inlineStr">
+        <is>
+          <t>情景</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>AOV改善</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="inlineStr">
+        <is>
+          <t>补贴压降</t>
+        </is>
+      </c>
+      <c r="D11" s="36" t="inlineStr">
+        <is>
+          <t>高价值用户↑</t>
+        </is>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>履约成本↓</t>
+        </is>
+      </c>
+      <c r="F11" s="36" t="inlineStr">
+        <is>
+          <t>聚焦组EBIT改善</t>
+        </is>
+      </c>
+      <c r="G11" s="36" t="inlineStr">
+        <is>
+          <t>优化组EBIT改善</t>
+        </is>
+      </c>
+      <c r="H11" s="36" t="inlineStr">
+        <is>
+          <t>观察组变化</t>
+        </is>
+      </c>
+      <c r="I11" s="36" t="inlineStr">
+        <is>
+          <t>组合EBIT</t>
+        </is>
+      </c>
+      <c r="J11" s="36" t="inlineStr">
+        <is>
+          <t>置信度</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="B12" s="38" t="inlineStr">
+        <is>
+          <t>+2.0元</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>-0.5元</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="inlineStr">
+        <is>
+          <t>+3pp</t>
+        </is>
+      </c>
+      <c r="E12" s="38" t="inlineStr">
+        <is>
+          <t>-0.2元</t>
+        </is>
+      </c>
+      <c r="F12" s="38" t="inlineStr">
+        <is>
+          <t>+3,500万</t>
+        </is>
+      </c>
+      <c r="G12" s="38" t="inlineStr">
+        <is>
+          <t>+2,000万</t>
+        </is>
+      </c>
+      <c r="H12" s="38" t="inlineStr">
+        <is>
+          <t>-1,500万</t>
+        </is>
+      </c>
+      <c r="I12" s="38" t="inlineStr">
+        <is>
+          <t>+4,000万</t>
+        </is>
+      </c>
+      <c r="J12" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>基准</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>+3.5元</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>-0.8元</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
+        <is>
+          <t>+5pp</t>
+        </is>
+      </c>
+      <c r="E13" s="43" t="inlineStr">
+        <is>
+          <t>-0.4元</t>
+        </is>
+      </c>
+      <c r="F13" s="43" t="inlineStr">
+        <is>
+          <t>+5,000万</t>
+        </is>
+      </c>
+      <c r="G13" s="43" t="inlineStr">
+        <is>
+          <t>+3,500万</t>
+        </is>
+      </c>
+      <c r="H13" s="43" t="inlineStr">
+        <is>
+          <t>-1,800万</t>
+        </is>
+      </c>
+      <c r="I13" s="43" t="inlineStr">
+        <is>
+          <t>+6,700万</t>
+        </is>
+      </c>
+      <c r="J13" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>乐观</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>+5.0元</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>-1.2元</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="inlineStr">
+        <is>
+          <t>+8pp</t>
+        </is>
+      </c>
+      <c r="E14" s="43" t="inlineStr">
+        <is>
+          <t>-0.6元</t>
+        </is>
+      </c>
+      <c r="F14" s="43" t="inlineStr">
+        <is>
+          <t>+7,000万</t>
+        </is>
+      </c>
+      <c r="G14" s="43" t="inlineStr">
+        <is>
+          <t>+5,000万</t>
+        </is>
+      </c>
+      <c r="H14" s="43" t="inlineStr">
+        <is>
+          <t>-2,200万</t>
+        </is>
+      </c>
+      <c r="I14" s="43" t="inlineStr">
+        <is>
+          <t>+9,800万</t>
+        </is>
+      </c>
+      <c r="J14" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="8" customHeight="1"/>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>SECTION 3: 3年EBIT桥（基准情景）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B17" s="36" t="inlineStr">
+        <is>
+          <t>当前</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="D17" s="36" t="inlineStr">
+        <is>
+          <t>Year 2</t>
+        </is>
+      </c>
+      <c r="E17" s="36" t="inlineStr">
+        <is>
+          <t>Year 3</t>
+        </is>
+      </c>
+      <c r="F17" s="36" t="inlineStr">
+        <is>
+          <t>累计改善</t>
+        </is>
+      </c>
+      <c r="G17" s="36" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="H17" s="36" t="inlineStr"/>
+      <c r="I17" s="36" t="inlineStr"/>
+      <c r="J17" s="36" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="38" t="inlineStr">
+        <is>
+          <t>聚焦组EBIT(万)</t>
+        </is>
+      </c>
+      <c r="B18" s="42" t="n">
+        <v>-500</v>
+      </c>
+      <c r="C18" s="42" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D18" s="42" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E18" s="42" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F18" s="42" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G18" s="42" t="inlineStr">
+        <is>
+          <t>3城：泉州已盈亏平衡，惠州+威海 Year1 贡献</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t>优化组EBIT(万)</t>
+        </is>
+      </c>
+      <c r="B19" s="42" t="n">
+        <v>-4500</v>
+      </c>
+      <c r="C19" s="42" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="D19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="42" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F19" s="42" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G19" s="42" t="inlineStr">
+        <is>
+          <t>徐州+南昌+南宁：Year 2 盈亏平衡</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="38" t="inlineStr">
+        <is>
+          <t>观察组EBIT(万)</t>
+        </is>
+      </c>
+      <c r="B20" s="42" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="C20" s="42" t="n">
+        <v>-4500</v>
+      </c>
+      <c r="D20" s="42" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="E20" s="42" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="F20" s="42" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="G20" s="42" t="inlineStr">
+        <is>
+          <t>收缩节省+部分城市退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t>总部固定成本(万)</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="C21" s="42" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="D21" s="42" t="n">
+        <v>-3800</v>
+      </c>
+      <c r="E21" s="42" t="n">
+        <v>-3500</v>
+      </c>
+      <c r="F21" s="42" t="n">
+        <v>-15300</v>
+      </c>
+      <c r="G21" s="42" t="inlineStr">
+        <is>
+          <t>固定成本分摊减少（收缩城市）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="47" t="inlineStr">
+        <is>
+          <t>组合EBIT(万)</t>
+        </is>
+      </c>
+      <c r="B22" s="48" t="n">
+        <v>-14000</v>
+      </c>
+      <c r="C22" s="48" t="n">
+        <v>-5500</v>
+      </c>
+      <c r="D22" s="48" t="n">
+        <v>-3300</v>
+      </c>
+      <c r="E22" s="48" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F22" s="49" t="n">
+        <v>-13800</v>
+      </c>
+      <c r="G22" s="49" t="inlineStr">
+        <is>
+          <t>Year 3 整体EBIT转正</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t>vs 上年(万)</t>
+        </is>
+      </c>
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" s="42" t="inlineStr">
+        <is>
+          <t>+8,500</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="inlineStr">
+        <is>
+          <t>+2,200</t>
+        </is>
+      </c>
+      <c r="E23" s="42" t="inlineStr">
+        <is>
+          <t>+5,300</t>
+        </is>
+      </c>
+      <c r="F23" s="42" t="inlineStr"/>
+      <c r="G23" s="42" t="inlineStr"/>
+    </row>
+    <row r="24" ht="8" customHeight="1"/>
+    <row r="25">
+      <c r="A25" s="35" t="inlineStr">
+        <is>
+          <t>SECTION 4: 关键洞察</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>基准情景 Year 2 组合EBIT转正（+3,300万）—— 3+3+4 策略可行</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="43" t="inlineStr">
+        <is>
+          <t>保守情景 Year 3 勉强EBIT转正（+2,000万）—— 下行风险可控</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="inlineStr">
+        <is>
+          <t>乐观情景 Year 2 即锁定EBIT+（+7,000万）—— 上行空间显著</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>关键假设：AOV年增+3.5元 + 补贴年压降-0.8元 + 高价值用户+5pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>约束条件：聚焦组 3城（泉州/惠州/威海）必须率先EBIT+，否则整体策略失效</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="8" customHeight="1"/>
+    <row r="32">
+      <c r="A32" s="35" t="inlineStr">
+        <is>
+          <t>SECTION 5: 敏感性分析（Year 3 组合EBIT，保守情景为基准）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="36" t="inlineStr"/>
+      <c r="B33" s="36" t="inlineStr">
+        <is>
+          <t>AOV-1元</t>
+        </is>
+      </c>
+      <c r="C33" s="36" t="inlineStr">
+        <is>
+          <t>AOV基准</t>
+        </is>
+      </c>
+      <c r="D33" s="36" t="inlineStr">
+        <is>
+          <t>AOV+1元</t>
+        </is>
+      </c>
+      <c r="E33" s="36" t="inlineStr"/>
+      <c r="F33" s="36" t="inlineStr">
+        <is>
+          <t>补贴+0.5元</t>
+        </is>
+      </c>
+      <c r="G33" s="36" t="inlineStr">
+        <is>
+          <t>补贴基准</t>
+        </is>
+      </c>
+      <c r="H33" s="36" t="inlineStr">
+        <is>
+          <t>补贴-0.5元</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t>保守情景</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n">
+        <v>-500</v>
+      </c>
+      <c r="C34" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="50" t="n">
+        <v>500</v>
+      </c>
+      <c r="E34" s="42" t="inlineStr"/>
+      <c r="F34" s="50" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G34" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="50" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="37" t="inlineStr">
+        <is>
+          <t>基准情景</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C35" s="50" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D35" s="50" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E35" s="42" t="inlineStr"/>
+      <c r="F35" s="50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G35" s="50" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H35" s="50" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="37" t="inlineStr">
+        <is>
+          <t>乐观情景</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C36" s="50" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D36" s="50" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E36" s="42" t="inlineStr"/>
+      <c r="F36" s="50" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G36" s="50" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H36" s="50" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="37" ht="8" customHeight="1"/>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>数据来源：01-problem-definition.md (CSO估算) | 情景假设：基于 03-priority-matrix.md 情景框架 | 补贴压降空间：基于 AX-B3 竞争情景分析</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="B30:J30"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>